--- a/docs/downloads/04/tbl_class_alaotra_ambatomanga.xlsx
+++ b/docs/downloads/04/tbl_class_alaotra_ambatomanga.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -486,14 +486,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>12.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -555,14 +549,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>18.6</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="10">
@@ -573,19 +567,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>4.7</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -601,14 +589,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>50</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -619,7 +601,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -628,10 +610,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +629,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <v>15.6</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -670,37 +646,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>81.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="E15">
-        <v>3.1</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -716,14 +692,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D16">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E16">
-        <v>70.40000000000001</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -739,14 +715,8 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>49</v>
-      </c>
-      <c r="E17">
-        <v>29</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -757,19 +727,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E18">
-        <v>0.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="19">
@@ -785,14 +755,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D19">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E19">
-        <v>49.5</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="20">
@@ -808,14 +778,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D20">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E20">
-        <v>41.2</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -826,19 +796,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E21">
-        <v>9.300000000000001</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="22">
@@ -854,14 +824,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D22">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="E22">
-        <v>46.3</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="23">
@@ -877,14 +847,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D23">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="E23">
-        <v>34.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="24">
@@ -895,19 +865,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D24">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E24">
-        <v>17.4</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="25">
@@ -918,19 +888,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>5</v>
-      </c>
-      <c r="E25">
-        <v>1.8</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -946,7 +910,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D26">
@@ -964,19 +928,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>17</v>
-      </c>
-      <c r="E27">
-        <v>43.6</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -987,19 +945,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>185</v>
       </c>
       <c r="E28">
-        <v>2.6</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="29">
@@ -1015,14 +973,8 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>28</v>
-      </c>
-      <c r="E29">
-        <v>12.9</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1038,37 +990,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D30">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="E30">
-        <v>85.3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>6-10 ans</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>4</v>
-      </c>
-      <c r="E31">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
